--- a/config/AudioConfig.xlsx
+++ b/config/AudioConfig.xlsx
@@ -779,7 +779,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>imported</t>
         </is>
       </c>
       <c r="H3" s="2" t="b">
@@ -817,12 +817,12 @@
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>中速战斗循环；鼓点清楚但不要过密，给部署、命中和法术音效留空间。</t>
+          <t>三国战斗循环：古筝+笛动作节奏（热血物语向），鼓点中速给部署/命中音效留空间；后续按 A3 换定制曲。</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
-          <t>未入库；待制作/采购音频文件</t>
+          <t>占位正式曲：Ninja Theme by Spring Spring，OpenGameArt CC0（公共领域，可商用免署名）；OGG 原文件入库。</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>res://sound/bgm/music_main_menu.ogg</t>
+          <t>res://sound/bgm/music_main_menu.wav</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>imported</t>
         </is>
       </c>
       <c r="H4" s="2" t="b">
@@ -897,12 +897,12 @@
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>黑暗中世纪身份主题；低弦乐、框鼓、远钟和微弱唱诗，先把世界观立住。</t>
+          <t>三国主菜单主题：宁静东方古韵（古筝/笛类音色），先立氛围；后续按 A3 音频方向换正式定制曲。</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>未入库；待制作/采购音频文件</t>
+          <t>占位正式曲：Oriental by Shadowfire452，OpenGameArt CC0（公共领域，可商用免署名）；WAV 原格式入库。</t>
         </is>
       </c>
     </row>

--- a/config/AudioConfig.xlsx
+++ b/config/AudioConfig.xlsx
@@ -12,7 +12,7 @@
     <sheet name="_Enums" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AudioAssets'!$A$1:$R$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AudioAssets'!$A$1:$R$82</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ColumnGuide'!$A$1:$D$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -551,7 +551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R80"/>
+  <dimension ref="A1:R82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -749,12 +749,12 @@
     <row r="3" ht="42" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>music_battle_normal</t>
+          <t>music_battle_hunt</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>常规战斗循环</t>
+          <t>战斗轮播曲B</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>res://sound/bgm/music_battle_normal.ogg</t>
+          <t>res://sound/bgm/dentaneosuchus_hunt.mp3</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="H3" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2" t="n">
         <v>-10</v>
@@ -817,24 +817,24 @@
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>三国战斗循环：古筝+笛动作节奏（热血物语向），鼓点中速给部署/命中音效留空间；后续按 A3 换定制曲。</t>
+          <t>战斗轮播集曲目B：与 music_battle_normal 轮番随机播放（loop=false 刻意为之，勿改回 true）。</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
-          <t>占位正式曲：Ninja Theme by Spring Spring，OpenGameArt CC0（公共领域，可商用免署名）；OGG 原文件入库。</t>
+          <t>正式曲 0716 批次：Dentaneosuchus Hunt（用户提供 mp3）。</t>
         </is>
       </c>
     </row>
     <row r="4" ht="42" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>music_main_menu</t>
+          <t>music_battle_normal</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>主菜单主题曲</t>
+          <t>常规战斗循环</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>menu</t>
+          <t>battle</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>res://sound/bgm/music_main_menu.wav</t>
+          <t>res://sound/bgm/sauropod_spotting.mp3</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -863,10 +863,10 @@
         </is>
       </c>
       <c r="H4" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>1</v>
@@ -878,11 +878,11 @@
         <v>1</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>45-75</t>
+          <t>60-90</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -892,29 +892,29 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>main_menu _ready</t>
+          <t>normal battle _ready</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>三国主菜单主题：宁静东方古韵（古筝/笛类音色），先立氛围；后续按 A3 音频方向换正式定制曲。</t>
+          <t>战斗轮播集曲目A：与 music_battle_hunt 轮番随机播放（loop=false 刻意为之，曲终触发轮播换曲，勿改回 true）。</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>占位正式曲：Oriental by Shadowfire452，OpenGameArt CC0（公共领域，可商用免署名）；WAV 原格式入库。</t>
+          <t>正式曲 0716 批次：Sauropod Spotting（用户提供 mp3）。</t>
         </is>
       </c>
     </row>
     <row r="5" ht="42" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>music_reward_ambient</t>
+          <t>music_deck_prep</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>奖励界面氛围音乐</t>
+          <t>战前选卡上阵曲</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>reward</t>
+          <t>menu</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -934,19 +934,19 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>res://sound/bgm/music_reward_ambient.ogg</t>
+          <t>res://sound/bgm/heroic_demise.mp3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>imported</t>
         </is>
       </c>
       <c r="H5" s="2" t="b">
         <v>1</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-13</v>
+        <v>-9</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>1</v>
@@ -958,43 +958,43 @@
         <v>1</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20-40</t>
+          <t>45-75</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>reward overlay open</t>
+          <t>deck_builder _ready</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>神秘奖励底音；如果 run 地图音乐已经能承托奖励界面，可后续取消或弱化。</t>
+          <t>战前选卡上阵界面（deck_builder，PVE 上阵与天梯选卡组共用）：Heroic Demise，循环播放。</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>未入库；待制作/采购音频文件</t>
+          <t>正式曲 0716 批次：Heroic Demise (New)（用户提供 mp3）。</t>
         </is>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>music_run_map</t>
+          <t>music_main_menu</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Roguelite 地图音乐</t>
+          <t>主菜单主题曲</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>run</t>
+          <t>menu</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1014,19 +1014,19 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>res://sound/bgm/music_run_map.ogg</t>
+          <t>res://sound/bgm/snowland.mp3</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>planned</t>
+          <t>imported</t>
         </is>
       </c>
       <c r="H6" s="2" t="b">
         <v>1</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>-11</v>
+        <v>-9</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>1</v>
@@ -1038,7 +1038,7 @@
         <v>1</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
@@ -1047,34 +1047,34 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>run_scene _ready</t>
+          <t>main_menu _ready</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>旅途/节点地图循环；克制、阴郁，有篝火、夜路和远方钟声的感觉。</t>
+          <t>主菜单默认曲：Snowland，循环播放；登录/创号/基地/图鉴/卡详情/闯关地图共用。</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>未入库；待制作/采购音频文件</t>
+          <t>正式曲 0716 批次：Snowland（用户提供 mp3 原格式入库，替换原 Oriental 占位曲）。</t>
         </is>
       </c>
     </row>
     <row r="7" ht="42" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>music_tutorial</t>
+          <t>music_reward_ambient</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>教学/短战役音乐</t>
+          <t>奖励界面氛围音乐</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>campaign</t>
+          <t>reward</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>res://sound/bgm/music_tutorial.ogg</t>
+          <t>res://sound/bgm/music_reward_ambient.ogg</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1106,7 +1106,7 @@
         <v>1</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>1</v>
@@ -1118,26 +1118,26 @@
         <v>1</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>45-75</t>
+          <t>20-40</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>future tutorial/campaign</t>
+          <t>reward overlay open</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>教学用安静循环；紧张度低于战斗音乐，避免干扰新手理解操作。</t>
+          <t>神秘奖励底音；如果 run 地图音乐已经能承托奖励界面，可后续取消或弱化。</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
@@ -1149,32 +1149,32 @@
     <row r="8" ht="42" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>amb_battle_wind</t>
+          <t>music_run_map</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>战场风声环境</t>
+          <t>Roguelite 地图音乐</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>ambience</t>
+          <t>music</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>battle</t>
+          <t>run</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Ambience</t>
+          <t>Music</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>res://sound/ambience/amb_battle_wind.ogg</t>
+          <t>res://sound/bgm/music_run_map.ogg</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1186,7 +1186,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>-22</v>
+        <v>-11</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>1</v>
@@ -1198,11 +1198,11 @@
         <v>1</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>30-60</t>
+          <t>45-75</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1212,12 +1212,12 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>battle ambience layer</t>
+          <t>run_scene _ready</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>低音量风声、远处旗帜和空旷战场气氛；必须很轻，不能盖住玩法反馈。</t>
+          <t>旅途/节点地图循环；克制、阴郁，有篝火、夜路和远方钟声的感觉。</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
@@ -1229,32 +1229,32 @@
     <row r="9" ht="42" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>amb_run_campfire</t>
+          <t>music_tutorial</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>营地篝火环境</t>
+          <t>教学/短战役音乐</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>ambience</t>
+          <t>music</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>run</t>
+          <t>campaign</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Ambience</t>
+          <t>Music</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>res://sound/ambience/amb_run_campfire.ogg</t>
+          <t>res://sound/bgm/music_tutorial.ogg</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1266,7 +1266,7 @@
         <v>1</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>-24</v>
+        <v>-12</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>1</v>
@@ -1278,11 +1278,11 @@
         <v>1</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>30-60</t>
+          <t>45-75</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1292,12 +1292,12 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>run map ambience layer</t>
+          <t>future tutorial/campaign</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>篝火、远钟、夜风；作为 run 地图音乐下的可选环境层。</t>
+          <t>教学用安静循环；紧张度低于战斗音乐，避免干扰新手理解操作。</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
@@ -1309,17 +1309,17 @@
     <row r="10" ht="42" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>stinger_battle_start</t>
+          <t>amb_battle_wind</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>战斗开始短乐句</t>
+          <t>战场风声环境</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>stinger</t>
+          <t>ambience</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>SFX</t>
+          <t>Ambience</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>res://sound/stingers/stinger_battle_start.wav</t>
+          <t>res://sound/ambience/amb_battle_wind.ogg</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1343,10 +1343,10 @@
         </is>
       </c>
       <c r="H10" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>-5</v>
+        <v>-22</v>
       </c>
       <c r="J10" s="2" t="n">
         <v>1</v>
@@ -1358,11 +1358,11 @@
         <v>1</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>30-60</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>battle starts</t>
+          <t>battle ambience layer</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>短鼓点或号角吸气，提示对局开始；不要拖太长，避免压住首轮出牌。</t>
+          <t>低音量风声、远处旗帜和空旷战场气氛；必须很轻，不能盖住玩法反馈。</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
@@ -1389,32 +1389,32 @@
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>stinger_defeat</t>
+          <t>amb_run_campfire</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>失败短乐句</t>
+          <t>营地篝火环境</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>stinger</t>
+          <t>ambience</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>result</t>
+          <t>run</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>SFX</t>
+          <t>Ambience</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>res://sound/stingers/stinger_defeat.wav</t>
+          <t>res://sound/ambience/amb_run_campfire.ogg</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1423,10 +1423,10 @@
         </is>
       </c>
       <c r="H11" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>-4</v>
+        <v>-24</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>1</v>
@@ -1438,26 +1438,26 @@
         <v>1</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2-4</t>
+          <t>30-60</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>player lose result</t>
+          <t>run map ambience layer</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>下行低钟和鼓点；黑暗但不要刺耳，避免失败后反复听产生烦躁。</t>
+          <t>篝火、远钟、夜风；作为 run 地图音乐下的可选环境层。</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
     <row r="12" ht="42" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>stinger_draw</t>
+          <t>stinger_battle_start</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>平局短乐句</t>
+          <t>战斗开始短乐句</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>result</t>
+          <t>battle</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>res://sound/stingers/stinger_draw.wav</t>
+          <t>res://sound/stingers/stinger_battle_start.wav</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1518,11 +1518,11 @@
         <v>1</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1.5-3</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>draw result</t>
+          <t>battle starts</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>中性、未解决的收束；表达没赢也没输的悬置感。</t>
+          <t>短鼓点或号角吸气，提示对局开始；不要拖太长，避免压住首轮出牌。</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
@@ -1549,12 +1549,12 @@
     <row r="13" ht="42" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>stinger_run_cleared</t>
+          <t>stinger_defeat</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>通关胜利短乐句</t>
+          <t>失败短乐句</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>res://sound/stingers/stinger_run_cleared.wav</t>
+          <t>res://sound/stingers/stinger_defeat.wav</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1586,7 +1586,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>1</v>
@@ -1602,22 +1602,22 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4-8</t>
+          <t>2-4</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>roguelite run won</t>
+          <t>player lose result</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>整局通关的大胜利乐句；比普通胜利更隆重，但仍要短，适合重复游玩。</t>
+          <t>下行低钟和鼓点；黑暗但不要刺耳，避免失败后反复听产生烦躁。</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
@@ -1629,12 +1629,12 @@
     <row r="14" ht="42" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>stinger_victory</t>
+          <t>stinger_draw</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>胜利短乐句</t>
+          <t>平局短乐句</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>res://sound/stingers/stinger_victory.wav</t>
+          <t>res://sound/stingers/stinger_draw.wav</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>1</v>
@@ -1678,26 +1678,26 @@
         <v>1</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2-4</t>
+          <t>1.5-3</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>player win result</t>
+          <t>draw result</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>清晰胜利收束；青铜钟、小合唱上扬，尾音短，适合频繁对局。</t>
+          <t>中性、未解决的收束；表达没赢也没输的悬置感。</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
@@ -1709,32 +1709,32 @@
     <row r="15" ht="42" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>ui_button_back</t>
+          <t>stinger_run_cleared</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>返回按钮</t>
+          <t>通关胜利短乐句</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>ui</t>
+          <t>stinger</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>ui</t>
+          <t>result</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>SFX</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>res://sound/ui/ui_button_back.wav</t>
+          <t>res://sound/stingers/stinger_run_cleared.wav</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1746,23 +1746,23 @@
         <v>0</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>-10</v>
+        <v>-3</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0.08-0.20</t>
+          <t>4-8</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>back/menu buttons</t>
+          <t>roguelite run won</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>更低、更软的返回点击或轻扫声，和普通确认点击区分。</t>
+          <t>整局通关的大胜利乐句；比普通胜利更隆重，但仍要短，适合重复游玩。</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
     <row r="16" ht="42" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>ui_button_press</t>
+          <t>stinger_victory</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>按钮点击</t>
+          <t>胜利短乐句</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>ui</t>
+          <t>stinger</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>ui</t>
+          <t>result</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>SFX</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>res://sound/ui/ui_button_press.wav</t>
+          <t>res://sound/stingers/stinger_victory.wav</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1826,23 +1826,23 @@
         <v>0</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>-9</v>
+        <v>-4</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0.05-0.15</t>
+          <t>2-4</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -1852,12 +1852,12 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>all button pressed</t>
+          <t>player win result</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>干燥木头/石质点击，快速确认 UI 操作。</t>
+          <t>清晰胜利收束；青铜钟、小合唱上扬，尾音短，适合频繁对局。</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
@@ -1869,12 +1869,12 @@
     <row r="17" ht="42" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>ui_card_cancel</t>
+          <t>ui_button_back</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>卡牌取消拖拽</t>
+          <t>返回按钮</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>card</t>
+          <t>ui</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>res://sound/ui/ui_card_cancel.wav</t>
+          <t>res://sound/ui/ui_button_back.wav</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1915,14 +1915,14 @@
         <v>1.02</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0.05-0.15</t>
+          <t>0.08-0.20</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>card released outside field</t>
+          <t>back/menu buttons</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>柔和的卡牌回手声，提示没有扣费也没有出牌。</t>
+          <t>更低、更软的返回点击或轻扫声，和普通确认点击区分。</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
     <row r="18" ht="42" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>ui_card_drop_invalid</t>
+          <t>ui_button_press</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>卡牌非法落下</t>
+          <t>按钮点击</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>card</t>
+          <t>ui</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>res://sound/ui/ui_card_drop_invalid.wav</t>
+          <t>res://sound/ui/ui_button_press.wav</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1992,17 +1992,17 @@
         <v>0.98</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0.08-0.20</t>
+          <t>0.05-0.15</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>illegal drop or no elixir</t>
+          <t>all button pressed</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>短促沉闷的受阻声；避免做成刺耳报错音。</t>
+          <t>干燥木头/石质点击，快速确认 UI 操作。</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
@@ -2029,12 +2029,12 @@
     <row r="19" ht="42" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>ui_card_drop_valid</t>
+          <t>ui_card_cancel</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>卡牌合法落下</t>
+          <t>卡牌取消拖拽</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>res://sound/ui/ui_card_drop_valid.wav</t>
+          <t>res://sound/ui/ui_card_cancel.wav</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2066,38 +2066,38 @@
         <v>0</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>-8</v>
+        <v>-10</v>
       </c>
       <c r="J19" s="2" t="n">
         <v>0.98</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0.08-0.20</t>
+          <t>0.05-0.15</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>card successfully played</t>
+          <t>card released outside field</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>正向的卡牌落位声；和部署/法术主音效叠加后仍要干净。</t>
+          <t>柔和的卡牌回手声，提示没有扣费也没有出牌。</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
     <row r="20" ht="42" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>ui_card_pickup</t>
+          <t>ui_card_drop_invalid</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>卡牌拿起</t>
+          <t>卡牌非法落下</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>res://sound/ui/ui_card_pickup.wav</t>
+          <t>res://sound/ui/ui_card_drop_invalid.wav</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2146,23 +2146,23 @@
         <v>0</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="J20" s="2" t="n">
         <v>0.98</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0.05-0.12</t>
+          <t>0.08-0.20</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>card drag begins</t>
+          <t>illegal drop or no elixir</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>卡牌从手牌抬起；清脆羊皮纸摩擦加很小的魔法点声。</t>
+          <t>短促沉闷的受阻声；避免做成刺耳报错音。</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
     <row r="21" ht="42" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>ui_language_switch</t>
+          <t>ui_card_drop_valid</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>语言切换</t>
+          <t>卡牌合法落下</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>settings</t>
+          <t>card</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>res://sound/ui/ui_language_switch.wav</t>
+          <t>res://sound/ui/ui_card_drop_valid.wav</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2226,38 +2226,38 @@
         <v>0</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0.15-0.30</t>
+          <t>0.08-0.20</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>language changed</t>
+          <t>card successfully played</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>轻微魔法翻页声，提示语言配置已切换。</t>
+          <t>正向的卡牌落位声；和部署/法术主音效叠加后仍要干净。</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
@@ -2269,12 +2269,12 @@
     <row r="22" ht="42" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>ui_panel_open</t>
+          <t>ui_card_pickup</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>面板打开</t>
+          <t>卡牌拿起</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>ui</t>
+          <t>card</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>res://sound/ui/ui_panel_open.wav</t>
+          <t>res://sound/ui/ui_card_pickup.wav</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2306,38 +2306,38 @@
         <v>0</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0.15-0.35</t>
+          <t>0.05-0.12</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>settings/reward/result panel appears</t>
+          <t>card drag begins</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>布料/羊皮纸展开加轻微提示音，用于设置、奖励、结算等面板。</t>
+          <t>卡牌从手牌抬起；清脆羊皮纸摩擦加很小的魔法点声。</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
@@ -2349,12 +2349,12 @@
     <row r="23" ht="42" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>ui_settings_toggle</t>
+          <t>ui_language_switch</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>设置开关</t>
+          <t>语言切换</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>res://sound/ui/ui_settings_toggle.wav</t>
+          <t>res://sound/ui/ui_language_switch.wav</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2386,7 +2386,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="J23" s="2" t="n">
         <v>1</v>
@@ -2395,14 +2395,14 @@
         <v>1</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>25</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0.05-0.15</t>
+          <t>0.15-0.30</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>settings toggles</t>
+          <t>language changed</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>很小的拨片/开关点击，用于设置项。</t>
+          <t>轻微魔法翻页声，提示语言配置已切换。</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
@@ -2429,12 +2429,12 @@
     <row r="24" ht="42" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>ui_volume_slide</t>
+          <t>ui_panel_open</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>音量滑条刻度</t>
+          <t>面板打开</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>settings</t>
+          <t>ui</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>res://sound/ui/ui_volume_slide.wav</t>
+          <t>res://sound/ui/ui_panel_open.wav</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -2466,7 +2466,7 @@
         <v>0</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>-14</v>
+        <v>-10</v>
       </c>
       <c r="J24" s="2" t="n">
         <v>1</v>
@@ -2478,26 +2478,26 @@
         <v>2</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>0.03-0.08</t>
+          <t>0.15-0.35</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>future volume slider</t>
+          <t>settings/reward/result panel appears</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>极轻的刻度 tick；如果后续接滑条，需要在代码里限频。</t>
+          <t>布料/羊皮纸展开加轻微提示音，用于设置、奖励、结算等面板。</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
@@ -2509,32 +2509,32 @@
     <row r="25" ht="42" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>elixir_full</t>
+          <t>ui_settings_toggle</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>圣水已满</t>
+          <t>设置开关</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>sfx</t>
+          <t>ui</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>elixir</t>
+          <t>settings</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>SFX</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>res://sound/sfx/elixir_full.wav</t>
+          <t>res://sound/ui/ui_settings_toggle.wav</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -2555,29 +2555,29 @@
         <v>1</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>0.25-0.50</t>
+          <t>0.05-0.15</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>elixir reaches max</t>
+          <t>settings toggles</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>轻微魔法充盈声；必须加冷却，不能满槽后反复触发。</t>
+          <t>很小的拨片/开关点击，用于设置项。</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
@@ -2589,32 +2589,32 @@
     <row r="26" ht="42" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>elixir_insufficient</t>
+          <t>ui_volume_slide</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>圣水不足</t>
+          <t>音量滑条刻度</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>sfx</t>
+          <t>ui</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>elixir</t>
+          <t>settings</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>SFX</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>res://sound/sfx/elixir_insufficient.wav</t>
+          <t>res://sound/ui/ui_volume_slide.wav</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2626,7 +2626,7 @@
         <v>0</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>-8</v>
+        <v>-14</v>
       </c>
       <c r="J26" s="2" t="n">
         <v>1</v>
@@ -2638,26 +2638,26 @@
         <v>2</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0.10-0.20</t>
+          <t>0.03-0.08</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>cannot afford card</t>
+          <t>future volume slider</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>空容器的干敲声；要和非法落点音区分。</t>
+          <t>极轻的刻度 tick；如果后续接滑条，需要在代码里限频。</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
@@ -2669,12 +2669,12 @@
     <row r="27" ht="42" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>elixir_spend</t>
+          <t>elixir_full</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>圣水消耗</t>
+          <t>圣水已满</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>res://sound/sfx/elixir_spend.wav</t>
+          <t>res://sound/sfx/elixir_full.wav</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -2706,38 +2706,38 @@
         <v>0</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>-8</v>
+        <v>-11</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0.10-0.25</t>
+          <t>0.25-0.50</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>card cost paid</t>
+          <t>elixir reaches max</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>魔法液体被抽走的声音，确认资源已支付。</t>
+          <t>轻微魔法充盈声；必须加冷却，不能满槽后反复触发。</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
     <row r="28" ht="42" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>elixir_tick</t>
+          <t>elixir_insufficient</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>圣水单格增长</t>
+          <t>圣水不足</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>res://sound/sfx/elixir_tick.wav</t>
+          <t>res://sound/sfx/elixir_insufficient.wav</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -2786,38 +2786,38 @@
         <v>0</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>-20</v>
+        <v>-8</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>0.03-0.08</t>
+          <t>0.10-0.20</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>optional individual pip gain</t>
+          <t>cannot afford card</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>很轻的单格增长提示；如果听感烦，可默认关闭。</t>
+          <t>空容器的干敲声；要和非法落点音区分。</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
@@ -2829,32 +2829,32 @@
     <row r="29" ht="42" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>run_boss_reveal</t>
+          <t>elixir_spend</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>首领节点揭示</t>
+          <t>圣水消耗</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>ui</t>
+          <t>sfx</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>run</t>
+          <t>elixir</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>SFX</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>res://sound/ui/run_boss_reveal.wav</t>
+          <t>res://sound/sfx/elixir_spend.wav</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -2866,38 +2866,38 @@
         <v>0</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M29" s="2" t="n">
         <v>70</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>0.50-1.20</t>
+          <t>0.10-0.25</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>boss node/reward appears</t>
+          <t>card cost paid</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>阴沉重击加钟声，用于 boss 节点或 boss 奖励出现。</t>
+          <t>魔法液体被抽走的声音，确认资源已支付。</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
@@ -2909,32 +2909,32 @@
     <row r="30" ht="42" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>run_node_complete</t>
+          <t>elixir_tick</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>地图节点完成</t>
+          <t>圣水单格增长</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>ui</t>
+          <t>sfx</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>run</t>
+          <t>elixir</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>SFX</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>res://sound/ui/run_node_complete.wav</t>
+          <t>res://sound/sfx/elixir_tick.wav</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -2946,38 +2946,38 @@
         <v>0</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>-8</v>
+        <v>-20</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>1</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>0.25-0.60</t>
+          <t>0.03-0.08</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>node marked completed</t>
+          <t>optional individual pip gain</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>蜡封盖章或小胜利标记声，确认节点已清。</t>
+          <t>很轻的单格增长提示；如果听感烦，可默认关闭。</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
     <row r="31" ht="42" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>run_node_select</t>
+          <t>run_boss_reveal</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>地图节点选择</t>
+          <t>首领节点揭示</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>res://sound/ui/run_node_select.wav</t>
+          <t>res://sound/ui/run_boss_reveal.wav</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3026,7 +3026,7 @@
         <v>0</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>-9</v>
+        <v>-6</v>
       </c>
       <c r="J31" s="2" t="n">
         <v>1</v>
@@ -3035,14 +3035,14 @@
         <v>1</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>0.10-0.25</t>
+          <t>0.50-1.20</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>run node highlighted/selected</t>
+          <t>boss node/reward appears</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>地图棋子/标记落在羊皮纸上的点击声。</t>
+          <t>阴沉重击加钟声，用于 boss 节点或 boss 奖励出现。</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
@@ -3069,12 +3069,12 @@
     <row r="32" ht="42" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>reward_card_pick</t>
+          <t>run_node_complete</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>选择奖励卡</t>
+          <t>地图节点完成</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>reward</t>
+          <t>run</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>res://sound/ui/reward_card_pick.wav</t>
+          <t>res://sound/ui/run_node_complete.wav</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3106,7 +3106,7 @@
         <v>0</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>1</v>
@@ -3118,26 +3118,26 @@
         <v>1</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>0.35-0.80</t>
+          <t>0.25-0.60</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>draft card chosen</t>
+          <t>node marked completed</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>正向魔法锁定声；应让玩家觉得这次选择有价值。</t>
+          <t>蜡封盖章或小胜利标记声，确认节点已清。</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
     <row r="33" ht="42" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>reward_card_reveal</t>
+          <t>run_node_select</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>奖励卡牌揭示</t>
+          <t>地图节点选择</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>reward</t>
+          <t>run</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>res://sound/ui/reward_card_reveal.wav</t>
+          <t>res://sound/ui/run_node_select.wav</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -3189,20 +3189,20 @@
         <v>-9</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>0.15-0.35</t>
+          <t>0.10-0.25</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
@@ -3212,12 +3212,12 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>each draft card pops in</t>
+          <t>run node highlighted/selected</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>短卡牌翻面声，适合三张卡错峰出现。</t>
+          <t>地图棋子/标记落在羊皮纸上的点击声。</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
@@ -3229,12 +3229,12 @@
     <row r="34" ht="42" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>reward_panel_open</t>
+          <t>reward_card_pick</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>奖励面板打开</t>
+          <t>选择奖励卡</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>res://sound/ui/reward_panel_open.wav</t>
+          <t>res://sound/ui/reward_card_pick.wav</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -3266,7 +3266,7 @@
         <v>0</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>1</v>
@@ -3278,11 +3278,11 @@
         <v>1</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>0.25-0.60</t>
+          <t>0.35-0.80</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
@@ -3292,12 +3292,12 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>reward panel opens</t>
+          <t>draft card chosen</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>羊皮纸展开加魔法微光，提示战后奖励出现。</t>
+          <t>正向魔法锁定声；应让玩家觉得这次选择有价值。</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
     <row r="35" ht="42" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>reward_skip</t>
+          <t>reward_card_reveal</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>跳过奖励</t>
+          <t>奖励卡牌揭示</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>res://sound/ui/reward_skip.wav</t>
+          <t>res://sound/ui/reward_card_reveal.wav</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -3346,23 +3346,23 @@
         <v>0</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>0.10-0.25</t>
+          <t>0.15-0.35</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>reward skipped</t>
+          <t>each draft card pops in</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>柔和关闭声，不要带失败或惩罚情绪。</t>
+          <t>短卡牌翻面声，适合三张卡错峰出现。</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
@@ -3389,12 +3389,12 @@
     <row r="36" ht="42" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>relic_pick</t>
+          <t>reward_panel_open</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>选择遗物</t>
+          <t>奖励面板打开</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>res://sound/ui/relic_pick.wav</t>
+          <t>res://sound/ui/reward_panel_open.wav</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -3426,7 +3426,7 @@
         <v>0</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="J36" s="2" t="n">
         <v>1</v>
@@ -3438,11 +3438,11 @@
         <v>1</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>0.50-1.00</t>
+          <t>0.25-0.60</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>relic chosen</t>
+          <t>reward panel opens</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>黑暗魔法封印声；要让玩家记住这次强化。</t>
+          <t>羊皮纸展开加魔法微光，提示战后奖励出现。</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
@@ -3469,12 +3469,12 @@
     <row r="37" ht="42" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>relic_reveal</t>
+          <t>reward_skip</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>遗物揭示</t>
+          <t>跳过奖励</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>res://sound/ui/relic_reveal.wav</t>
+          <t>res://sound/ui/reward_skip.wav</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -3506,7 +3506,7 @@
         <v>0</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>-7</v>
+        <v>-10</v>
       </c>
       <c r="J37" s="2" t="n">
         <v>1</v>
@@ -3515,29 +3515,29 @@
         <v>1</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>0.45-0.90</t>
+          <t>0.10-0.25</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>relic offer appears</t>
+          <t>reward skipped</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>古物微光声，比普通卡牌更有仪式感。</t>
+          <t>柔和关闭声，不要带失败或惩罚情绪。</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
     <row r="38" ht="42" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>meta_unlock</t>
+          <t>relic_pick</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>局间解锁</t>
+          <t>选择遗物</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>run</t>
+          <t>reward</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>res://sound/ui/meta_unlock.wav</t>
+          <t>res://sound/ui/relic_pick.wav</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -3602,22 +3602,22 @@
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>0.80-1.50</t>
+          <t>0.50-1.00</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>new relic/meta unlock</t>
+          <t>relic chosen</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>较大的解锁音效；稀有、满足，但不要像胜利音乐一样拖长。</t>
+          <t>黑暗魔法封印声；要让玩家记住这次强化。</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
@@ -3629,32 +3629,32 @@
     <row r="39" ht="42" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>deploy_air</t>
+          <t>relic_reveal</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>空中单位部署</t>
+          <t>遗物揭示</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>sfx</t>
+          <t>ui</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>deploy</t>
+          <t>reward</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>SFX</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>res://sound/sfx/deploy_air.wav</t>
+          <t>res://sound/ui/relic_reveal.wav</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -3666,38 +3666,38 @@
         <v>0</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>0.20-0.45</t>
+          <t>0.45-0.90</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>flying troop spawn</t>
+          <t>relic offer appears</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>幽魂升起或气流声，适合飞兵和火颅，不要做成真实鸟翼。</t>
+          <t>古物微光声，比普通卡牌更有仪式感。</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
@@ -3709,32 +3709,32 @@
     <row r="40" ht="42" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>deploy_death_spawn</t>
+          <t>meta_unlock</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>亡语召唤</t>
+          <t>局间解锁</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>sfx</t>
+          <t>ui</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>deploy</t>
+          <t>run</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>SFX</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>res://sound/sfx/deploy_death_spawn.wav</t>
+          <t>res://sound/ui/meta_unlock.wav</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -3746,38 +3746,38 @@
         <v>0</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>0.25-0.55</t>
+          <t>0.80-1.50</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>death_spawn units appear</t>
+          <t>new relic/meta unlock</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>尸体裂开、骨片和暗影爆开的混合声，用于 death_spawn。</t>
+          <t>较大的解锁音效；稀有、满足，但不要像胜利音乐一样拖长。</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
@@ -3789,12 +3789,12 @@
     <row r="41" ht="42" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>deploy_large</t>
+          <t>deploy_air</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>大型单位部署</t>
+          <t>空中单位部署</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>res://sound/sfx/deploy_large.wav</t>
+          <t>res://sound/sfx/deploy_air.wav</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -3826,38 +3826,38 @@
         <v>0</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="L41" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>0.25-0.55</t>
+          <t>0.20-0.45</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>giant/golem spawn</t>
+          <t>flying troop spawn</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t>重踏地面加低频盔甲/石头共鸣，突出巨人和魔像重量。</t>
+          <t>幽魂升起或气流声，适合飞兵和火颅，不要做成真实鸟翼。</t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
     <row r="42" ht="42" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>deploy_medium</t>
+          <t>deploy_death_spawn</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>中型单位部署</t>
+          <t>亡语召唤</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>res://sound/sfx/deploy_medium.wav</t>
+          <t>res://sound/sfx/deploy_death_spawn.wav</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -3909,20 +3909,20 @@
         <v>-7</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>4</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>0.15-0.35</t>
+          <t>0.25-0.55</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>standard single troop spawn</t>
+          <t>death_spawn units appear</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>盔甲和靴子落地声，适合骑士、弓手、女巫等标准单位。</t>
+          <t>尸体裂开、骨片和暗影爆开的混合声，用于 death_spawn。</t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
     <row r="43" ht="42" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>deploy_small</t>
+          <t>deploy_large</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>小型单位部署</t>
+          <t>大型单位部署</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3974,7 +3974,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>res://sound/sfx/deploy_small.wav</t>
+          <t>res://sound/sfx/deploy_large.wav</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -3986,23 +3986,23 @@
         <v>0</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="J43" s="2" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>0.12-0.25</t>
+          <t>0.25-0.55</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>small troop groups spawn</t>
+          <t>giant/golem spawn</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t>轻脚步、布料或骨头小弹出声，适合骷髅、哥布林、亡魂等小群体。</t>
+          <t>重踏地面加低频盔甲/石头共鸣，突出巨人和魔像重量。</t>
         </is>
       </c>
       <c r="R43" s="2" t="inlineStr">
@@ -4029,12 +4029,12 @@
     <row r="44" ht="42" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>deploy_spell_cast</t>
+          <t>deploy_medium</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>通用法术释放</t>
+          <t>中型单位部署</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -4054,7 +4054,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>res://sound/sfx/deploy_spell_cast.wav</t>
+          <t>res://sound/sfx/deploy_medium.wav</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -4066,38 +4066,38 @@
         <v>0</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>4</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>0.10-0.25</t>
+          <t>0.15-0.35</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>generic spell release if card has no custom cast</t>
+          <t>standard single troop spawn</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>短促魔法释放底声；仅给没有专属 cast 的法术兜底。</t>
+          <t>盔甲和靴子落地声，适合骑士、弓手、女巫等标准单位。</t>
         </is>
       </c>
       <c r="R44" s="2" t="inlineStr">
@@ -4109,12 +4109,12 @@
     <row r="45" ht="42" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>attack_blade_small</t>
+          <t>deploy_small</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>小型快速刺击</t>
+          <t>小型单位部署</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>combat</t>
+          <t>deploy</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -4134,7 +4134,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>res://sound/sfx/attack_blade_small.wav</t>
+          <t>res://sound/sfx/deploy_small.wav</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -4146,38 +4146,38 @@
         <v>0</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="J45" s="2" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="L45" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>0.05-0.14</t>
+          <t>0.12-0.25</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>goblin/skeleton fast melee</t>
+          <t>small troop groups spawn</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>轻刺、短刀或骨爪声，适合哥布林/骷髅等快攻单位。</t>
+          <t>轻脚步、布料或骨头小弹出声，适合骷髅、哥布林、亡魂等小群体。</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
@@ -4189,12 +4189,12 @@
     <row r="46" ht="42" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>attack_heavy</t>
+          <t>deploy_spell_cast</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>重型挥击</t>
+          <t>通用法术释放</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>combat</t>
+          <t>deploy</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>res://sound/sfx/attack_heavy.wav</t>
+          <t>res://sound/sfx/deploy_spell_cast.wav</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -4226,38 +4226,38 @@
         <v>0</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="L46" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M46" s="2" t="n">
         <v>60</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>0.12-0.28</t>
+          <t>0.10-0.25</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>berserker/ogre/golem heavy swing</t>
+          <t>generic spell release if card has no custom cast</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>大幅度挥砍和重量感，命中前就能感觉到重击要来了。</t>
+          <t>短促魔法释放底声；仅给没有专属 cast 的法术兜底。</t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr">
@@ -4269,12 +4269,12 @@
     <row r="47" ht="42" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>attack_sword</t>
+          <t>attack_blade_small</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>标准剑击挥砍</t>
+          <t>小型快速刺击</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>res://sound/sfx/attack_sword.wav</t>
+          <t>res://sound/sfx/attack_blade_small.wav</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -4306,38 +4306,38 @@
         <v>0</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="J47" s="2" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="L47" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>0.08-0.18</t>
+          <t>0.05-0.14</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>knight/standard melee swing</t>
+          <t>goblin/skeleton fast melee</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
         <is>
-          <t>短金属挥砍声；主要表达攻击动作，命中感交给 hit 音效。</t>
+          <t>轻刺、短刀或骨爪声，适合哥布林/骷髅等快攻单位。</t>
         </is>
       </c>
       <c r="R47" s="2" t="inlineStr">
@@ -4349,12 +4349,12 @@
     <row r="48" ht="42" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>hit_armor</t>
+          <t>attack_heavy</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>护甲受击</t>
+          <t>重型挥击</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>res://sound/sfx/hit_armor.wav</t>
+          <t>res://sound/sfx/attack_heavy.wav</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -4386,38 +4386,38 @@
         <v>0</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="L48" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>0.08-0.20</t>
+          <t>0.12-0.28</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>armored unit hit</t>
+          <t>berserker/ogre/golem heavy swing</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>金属碰撞但不要太亮，避免高频刺耳。</t>
+          <t>大幅度挥砍和重量感，命中前就能感觉到重击要来了。</t>
         </is>
       </c>
       <c r="R48" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
     <row r="49" ht="42" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>hit_heavy</t>
+          <t>attack_sword</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>重度受击</t>
+          <t>标准剑击挥砍</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>res://sound/sfx/hit_heavy.wav</t>
+          <t>res://sound/sfx/attack_sword.wav</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -4466,23 +4466,23 @@
         <v>0</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>0.15-0.35</t>
+          <t>0.08-0.18</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
@@ -4492,12 +4492,12 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>big hit / fireball / heavy unit</t>
+          <t>knight/standard melee swing</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
         <is>
-          <t>低频冲击，配合顿帧和震屏表达大伤害。</t>
+          <t>短金属挥砍声；主要表达攻击动作，命中感交给 hit 音效。</t>
         </is>
       </c>
       <c r="R49" s="2" t="inlineStr">
@@ -4509,12 +4509,12 @@
     <row r="50" ht="42" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>hit_light</t>
+          <t>hit_armor</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>轻度受击</t>
+          <t>护甲受击</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>res://sound/sfx/hit_light.wav</t>
+          <t>res://sound/sfx/hit_armor.wav</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -4546,38 +4546,38 @@
         <v>0</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>-11</v>
+        <v>-9</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.95</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="L50" s="2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M50" s="2" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>0.04-0.12</t>
+          <t>0.08-0.20</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>minor unit damage</t>
+          <t>armored unit hit</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>轻微布料/身体命中声；会频繁播放，必须短且不抢耳。</t>
+          <t>金属碰撞但不要太亮，避免高频刺耳。</t>
         </is>
       </c>
       <c r="R50" s="2" t="inlineStr">
@@ -4589,12 +4589,12 @@
     <row r="51" ht="42" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>hit_medium</t>
+          <t>hit_heavy</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>中度受击</t>
+          <t>重度受击</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>res://sound/sfx/hit_medium.wav</t>
+          <t>res://sound/sfx/hit_heavy.wav</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -4626,23 +4626,23 @@
         <v>0</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="L51" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M51" s="2" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>0.08-0.18</t>
+          <t>0.15-0.35</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
@@ -4652,12 +4652,12 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>normal unit damage</t>
+          <t>big hit / fireball / heavy unit</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
         <is>
-          <t>肉感命中加少量盔甲元素，是大多数普通伤害的默认反馈。</t>
+          <t>低频冲击，配合顿帧和震屏表达大伤害。</t>
         </is>
       </c>
       <c r="R51" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
     <row r="52" ht="42" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>hit_tower</t>
+          <t>hit_light</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>防御塔受击</t>
+          <t>轻度受击</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>tower</t>
+          <t>combat</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -4694,7 +4694,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>res://sound/sfx/hit_tower.wav</t>
+          <t>res://sound/sfx/hit_light.wav</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -4706,23 +4706,23 @@
         <v>0</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>-8</v>
+        <v>-11</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="L52" s="2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>0.10-0.25</t>
+          <t>0.04-0.12</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>tower takes damage</t>
+          <t>minor unit damage</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>石头/木结构裂响，必须和单位受击区分。</t>
+          <t>轻微布料/身体命中声；会频繁播放，必须短且不抢耳。</t>
         </is>
       </c>
       <c r="R52" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
     <row r="53" ht="42" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>death_bone</t>
+          <t>hit_medium</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>骷髅死亡</t>
+          <t>中度受击</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>death</t>
+          <t>combat</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>res://sound/sfx/death_bone.wav</t>
+          <t>res://sound/sfx/hit_medium.wav</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -4789,20 +4789,20 @@
         <v>-9</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.95</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>1.08</v>
       </c>
       <c r="L53" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M53" s="2" t="n">
         <v>45</v>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>0.15-0.35</t>
+          <t>0.08-0.18</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>skeleton dies</t>
+          <t>normal unit damage</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
         <is>
-          <t>骨头散架和落地声。</t>
+          <t>肉感命中加少量盔甲元素，是大多数普通伤害的默认反馈。</t>
         </is>
       </c>
       <c r="R53" s="2" t="inlineStr">
@@ -4829,12 +4829,12 @@
     <row r="54" ht="42" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>death_large</t>
+          <t>hit_tower</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>大型单位死亡</t>
+          <t>防御塔受击</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>death</t>
+          <t>tower</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -4854,7 +4854,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>res://sound/sfx/death_large.wav</t>
+          <t>res://sound/sfx/hit_tower.wav</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -4866,23 +4866,23 @@
         <v>0</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="L54" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>0.35-0.80</t>
+          <t>0.10-0.25</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>large unit dies</t>
+          <t>tower takes damage</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
         <is>
-          <t>重物倒塌或石块坍塌，体现大型单位死亡重量。</t>
+          <t>石头/木结构裂响，必须和单位受击区分。</t>
         </is>
       </c>
       <c r="R54" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
     <row r="55" ht="42" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>death_small</t>
+          <t>death_bone</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>小型单位死亡</t>
+          <t>骷髅死亡</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>res://sound/sfx/death_small.wav</t>
+          <t>res://sound/sfx/death_bone.wav</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -4946,7 +4946,7 @@
         <v>0</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="J55" s="2" t="n">
         <v>0.95</v>
@@ -4972,12 +4972,12 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>small living unit dies</t>
+          <t>skeleton dies</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
         <is>
-          <t>快速倒地和布料声，不强调血腥。</t>
+          <t>骨头散架和落地声。</t>
         </is>
       </c>
       <c r="R55" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
     <row r="56" ht="42" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>death_spirit</t>
+          <t>death_large</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>幽魂死亡</t>
+          <t>大型单位死亡</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -5014,7 +5014,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>res://sound/sfx/death_spirit.wav</t>
+          <t>res://sound/sfx/death_large.wav</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -5026,38 +5026,38 @@
         <v>0</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>-10</v>
+        <v>-6</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.96</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="L56" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M56" s="2" t="n">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>0.20-0.45</t>
+          <t>0.35-0.80</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>wraith/fire skull dies</t>
+          <t>large unit dies</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
         <is>
-          <t>烟雾和灵体消散声，适合亡魂、火颅等。</t>
+          <t>重物倒塌或石块坍塌，体现大型单位死亡重量。</t>
         </is>
       </c>
       <c r="R56" s="2" t="inlineStr">
@@ -5069,12 +5069,12 @@
     <row r="57" ht="42" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>bow_shot</t>
+          <t>death_small</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>弓箭发射</t>
+          <t>小型单位死亡</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>projectile</t>
+          <t>death</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -5094,7 +5094,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>res://sound/sfx/bow_shot.wav</t>
+          <t>res://sound/sfx/death_small.wav</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -5109,7 +5109,7 @@
         <v>-10</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>1.08</v>
@@ -5122,7 +5122,7 @@
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>0.05-0.15</t>
+          <t>0.15-0.35</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>archer projectile fired</t>
+          <t>small living unit dies</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
         <is>
-          <t>弓弦声加箭矢掠风，用于弓手远程开火。</t>
+          <t>快速倒地和布料声，不强调血腥。</t>
         </is>
       </c>
       <c r="R57" s="2" t="inlineStr">
@@ -5149,12 +5149,12 @@
     <row r="58" ht="42" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>arrow_hit</t>
+          <t>death_spirit</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>箭矢命中</t>
+          <t>幽魂死亡</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -5164,7 +5164,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>projectile</t>
+          <t>death</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>res://sound/sfx/arrow_hit.wav</t>
+          <t>res://sound/sfx/death_spirit.wav</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -5186,23 +5186,23 @@
         <v>0</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="L58" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>0.05-0.15</t>
+          <t>0.20-0.45</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>arrow projectile impact</t>
+          <t>wraith/fire skull dies</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
         <is>
-          <t>小型插入或钝击声，作为箭矢落点反馈。</t>
+          <t>烟雾和灵体消散声，适合亡魂、火颅等。</t>
         </is>
       </c>
       <c r="R58" s="2" t="inlineStr">
@@ -5229,12 +5229,12 @@
     <row r="59" ht="42" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>magic_bolt_cast</t>
+          <t>bow_shot</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>魔法弹发射</t>
+          <t>弓箭发射</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -5254,7 +5254,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>res://sound/sfx/magic_bolt_cast.wav</t>
+          <t>res://sound/sfx/bow_shot.wav</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -5266,23 +5266,23 @@
         <v>0</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="J59" s="2" t="n">
         <v>0.96</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="L59" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M59" s="2" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>0.08-0.20</t>
+          <t>0.05-0.15</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
@@ -5292,12 +5292,12 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>musketeer/sorceress bolt fired</t>
+          <t>archer projectile fired</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
         <is>
-          <t>暗紫色魔法弹的短促弹射声，用于女巫/远程法师。</t>
+          <t>弓弦声加箭矢掠风，用于弓手远程开火。</t>
         </is>
       </c>
       <c r="R59" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
     <row r="60" ht="42" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>magic_bolt_hit</t>
+          <t>arrow_hit</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>魔法弹命中</t>
+          <t>箭矢命中</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>res://sound/sfx/magic_bolt_hit.wav</t>
+          <t>res://sound/sfx/arrow_hit.wav</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -5346,23 +5346,23 @@
         <v>0</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>-9</v>
+        <v>-11</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="L60" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M60" s="2" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>0.08-0.20</t>
+          <t>0.05-0.15</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>magic bolt impact</t>
+          <t>arrow projectile impact</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
         <is>
-          <t>小型奥术爆点声。</t>
+          <t>小型插入或钝击声，作为箭矢落点反馈。</t>
         </is>
       </c>
       <c r="R60" s="2" t="inlineStr">
@@ -5389,12 +5389,12 @@
     <row r="61" ht="42" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>fire_skull_shot</t>
+          <t>magic_bolt_cast</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>火颅投射物发射</t>
+          <t>魔法弹发射</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>res://sound/sfx/fire_skull_shot.wav</t>
+          <t>res://sound/sfx/magic_bolt_cast.wav</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -5426,38 +5426,38 @@
         <v>0</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="J61" s="2" t="n">
         <v>0.96</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="L61" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>0.10-0.25</t>
+          <t>0.08-0.20</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>baby_dragon/fire skull projectile</t>
+          <t>musketeer/sorceress bolt fired</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
         <is>
-          <t>小火焰喷吐声，不能盖过火球法术。</t>
+          <t>暗紫色魔法弹的短促弹射声，用于女巫/远程法师。</t>
         </is>
       </c>
       <c r="R61" s="2" t="inlineStr">
@@ -5469,12 +5469,12 @@
     <row r="62" ht="42" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>tower_destroy_king</t>
+          <t>magic_bolt_hit</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>王塔摧毁</t>
+          <t>魔法弹命中</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5484,7 +5484,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>tower</t>
+          <t>projectile</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -5494,7 +5494,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>res://sound/sfx/tower_destroy_king.wav</t>
+          <t>res://sound/sfx/magic_bolt_hit.wav</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -5506,38 +5506,38 @@
         <v>0</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>-3</v>
+        <v>-9</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="L62" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>1.2-2.5</t>
+          <t>0.08-0.20</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>king tower destroyed</t>
+          <t>magic bolt impact</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
         <is>
-          <t>更大的城堡坍塌声，并自然衔接胜负短乐句。</t>
+          <t>小型奥术爆点声。</t>
         </is>
       </c>
       <c r="R62" s="2" t="inlineStr">
@@ -5549,12 +5549,12 @@
     <row r="63" ht="42" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>tower_destroy_princess</t>
+          <t>fire_skull_shot</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>公主塔摧毁</t>
+          <t>火颅投射物发射</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5564,7 +5564,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>tower</t>
+          <t>projectile</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>res://sound/sfx/tower_destroy_princess.wav</t>
+          <t>res://sound/sfx/fire_skull_shot.wav</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -5586,38 +5586,38 @@
         <v>0</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>-4</v>
+        <v>-8</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="L63" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M63" s="2" t="n">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>0.8-1.5</t>
+          <t>0.10-0.25</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>princess tower destroyed</t>
+          <t>baby_dragon/fire skull projectile</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
         <is>
-          <t>石块坍塌、尘土和短火光，配合塔毁震屏。</t>
+          <t>小火焰喷吐声，不能盖过火球法术。</t>
         </is>
       </c>
       <c r="R63" s="2" t="inlineStr">
@@ -5629,12 +5629,12 @@
     <row r="64" ht="42" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>tower_king_shot</t>
+          <t>tower_destroy_king</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>王塔射击</t>
+          <t>王塔摧毁</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5654,7 +5654,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>res://sound/sfx/tower_king_shot.wav</t>
+          <t>res://sound/sfx/tower_destroy_king.wav</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -5666,38 +5666,38 @@
         <v>0</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>-8</v>
+        <v>-3</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="L64" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>0.10-0.25</t>
+          <t>1.2-2.5</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>king tower fires</t>
+          <t>king tower destroyed</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
         <is>
-          <t>更厚重的塔射击声，和公主塔区分主次。</t>
+          <t>更大的城堡坍塌声，并自然衔接胜负短乐句。</t>
         </is>
       </c>
       <c r="R64" s="2" t="inlineStr">
@@ -5709,12 +5709,12 @@
     <row r="65" ht="42" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>tower_princess_shot</t>
+          <t>tower_destroy_princess</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>公主塔射击</t>
+          <t>公主塔摧毁</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>res://sound/sfx/tower_princess_shot.wav</t>
+          <t>res://sound/sfx/tower_destroy_princess.wav</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -5746,23 +5746,23 @@
         <v>0</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>-9</v>
+        <v>-4</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="L65" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M65" s="2" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>0.08-0.18</t>
+          <t>0.8-1.5</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>princess tower fires</t>
+          <t>princess tower destroyed</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
         <is>
-          <t>弩机或小型床弩弹射声。</t>
+          <t>石块坍塌、尘土和短火光，配合塔毁震屏。</t>
         </is>
       </c>
       <c r="R65" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
     <row r="66" ht="42" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>spell_arrows_cast</t>
+          <t>tower_king_shot</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>箭雨释放</t>
+          <t>王塔射击</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5804,7 +5804,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>spell</t>
+          <t>tower</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -5814,7 +5814,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>res://sound/sfx/spell_arrows_cast.wav</t>
+          <t>res://sound/sfx/tower_king_shot.wav</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -5835,29 +5835,29 @@
         <v>1.04</v>
       </c>
       <c r="L66" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M66" s="2" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>0.12-0.30</t>
+          <t>0.10-0.25</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>arrows card released</t>
+          <t>king tower fires</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
         <is>
-          <t>一组弓弦齐发或箭矢出手声。</t>
+          <t>更厚重的塔射击声，和公主塔区分主次。</t>
         </is>
       </c>
       <c r="R66" s="2" t="inlineStr">
@@ -5869,12 +5869,12 @@
     <row r="67" ht="42" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>spell_arrows_impact</t>
+          <t>tower_princess_shot</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>箭雨命中</t>
+          <t>公主塔射击</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>spell</t>
+          <t>tower</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>res://sound/sfx/spell_arrows_impact.wav</t>
+          <t>res://sound/sfx/tower_princess_shot.wav</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -5906,23 +5906,23 @@
         <v>0</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="J67" s="2" t="n">
         <v>0.96</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>4</v>
       </c>
       <c r="M67" s="2" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>0.35-0.70</t>
+          <t>0.08-0.18</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>arrows hit area</t>
+          <t>princess tower fires</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
         <is>
-          <t>大量箭矢扎入地面、护甲和单位的密集命中声。</t>
+          <t>弩机或小型床弩弹射声。</t>
         </is>
       </c>
       <c r="R67" s="2" t="inlineStr">
@@ -5949,12 +5949,12 @@
     <row r="68" ht="42" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>spell_fireball_cast</t>
+          <t>spell_arrows_cast</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>火球释放</t>
+          <t>箭雨释放</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5974,7 +5974,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>res://sound/sfx/spell_fireball_cast.wav</t>
+          <t>res://sound/sfx/spell_arrows_cast.wav</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -5986,23 +5986,23 @@
         <v>0</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.98</v>
+        <v>0.96</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>4</v>
       </c>
       <c r="M68" s="2" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>0.15-0.35</t>
+          <t>0.12-0.30</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
@@ -6012,12 +6012,12 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>fireball card released</t>
+          <t>arrows card released</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
         <is>
-          <t>火焰点燃并投出的声音。</t>
+          <t>一组弓弦齐发或箭矢出手声。</t>
         </is>
       </c>
       <c r="R68" s="2" t="inlineStr">
@@ -6029,12 +6029,12 @@
     <row r="69" ht="42" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>spell_fireball_fly</t>
+          <t>spell_arrows_impact</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>火球飞行</t>
+          <t>箭雨命中</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>res://sound/sfx/spell_fireball_fly.wav</t>
+          <t>res://sound/sfx/spell_arrows_impact.wav</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -6066,38 +6066,38 @@
         <v>0</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>-11</v>
+        <v>-8</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.98</v>
+        <v>0.96</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="L69" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M69" s="2" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>0.25-0.60</t>
+          <t>0.35-0.70</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>fireball projectile travel</t>
+          <t>arrows hit area</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
         <is>
-          <t>短火焰呼啸；如果当前表现层是瞬发，可后续不启用。</t>
+          <t>大量箭矢扎入地面、护甲和单位的密集命中声。</t>
         </is>
       </c>
       <c r="R69" s="2" t="inlineStr">
@@ -6109,12 +6109,12 @@
     <row r="70" ht="42" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>spell_fireball_impact</t>
+          <t>spell_fireball_cast</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>火球爆炸</t>
+          <t>火球释放</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>res://sound/sfx/spell_fireball_impact.wav</t>
+          <t>res://sound/sfx/spell_fireball_cast.wav</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -6146,23 +6146,23 @@
         <v>0</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>1.03</v>
       </c>
       <c r="L70" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M70" s="2" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>0.5-1.0</t>
+          <t>0.15-0.35</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
@@ -6172,12 +6172,12 @@
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>fireball explosion</t>
+          <t>fireball card released</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
         <is>
-          <t>低频爆炸加火焰噼啪尾音，是高优先级玩法反馈。</t>
+          <t>火焰点燃并投出的声音。</t>
         </is>
       </c>
       <c r="R70" s="2" t="inlineStr">
@@ -6189,12 +6189,12 @@
     <row r="71" ht="42" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>spell_golem_death_spawn</t>
+          <t>spell_fireball_fly</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>魔像亡语召唤</t>
+          <t>火球飞行</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -6214,7 +6214,7 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>res://sound/sfx/spell_golem_death_spawn.wav</t>
+          <t>res://sound/sfx/spell_fireball_fly.wav</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -6226,38 +6226,38 @@
         <v>0</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>-5</v>
+        <v>-11</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="L71" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M71" s="2" t="n">
-        <v>90</v>
+        <v>35</v>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>0.6-1.2</t>
+          <t>0.25-0.60</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>golem death_spawn triggers</t>
+          <t>fireball projectile travel</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
         <is>
-          <t>大型坍塌后有小单位破出的声层，突出亡语触发。</t>
+          <t>短火焰呼啸；如果当前表现层是瞬发，可后续不启用。</t>
         </is>
       </c>
       <c r="R71" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
     <row r="72" ht="42" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>spell_heal_cast</t>
+          <t>spell_fireball_impact</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>治疗术释放</t>
+          <t>火球爆炸</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -6294,7 +6294,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>res://sound/sfx/spell_heal_cast.wav</t>
+          <t>res://sound/sfx/spell_fireball_impact.wav</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -6306,23 +6306,23 @@
         <v>0</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>-8</v>
+        <v>-4</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.98</v>
+        <v>0.96</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>3</v>
       </c>
       <c r="M72" s="2" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>0.20-0.45</t>
+          <t>0.5-1.0</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
@@ -6332,12 +6332,12 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>heal card released</t>
+          <t>fireball explosion</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
         <is>
-          <t>柔和的圣洁/绿色魔法展开声。</t>
+          <t>低频爆炸加火焰噼啪尾音，是高优先级玩法反馈。</t>
         </is>
       </c>
       <c r="R72" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
     <row r="73" ht="42" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>spell_heal_end</t>
+          <t>spell_golem_death_spawn</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>治疗结束</t>
+          <t>魔像亡语召唤</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -6374,7 +6374,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>res://sound/sfx/spell_heal_end.wav</t>
+          <t>res://sound/sfx/spell_golem_death_spawn.wav</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -6386,38 +6386,38 @@
         <v>0</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>2</v>
       </c>
       <c r="M73" s="2" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>0.20-0.40</t>
+          <t>0.6-1.2</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>future heal over-time ends</t>
+          <t>golem death_spawn triggers</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
         <is>
-          <t>柔和收束的微光声，供后续持续治疗版本使用。</t>
+          <t>大型坍塌后有小单位破出的声层，突出亡语触发。</t>
         </is>
       </c>
       <c r="R73" s="2" t="inlineStr">
@@ -6429,12 +6429,12 @@
     <row r="74" ht="42" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>spell_heal_tick</t>
+          <t>spell_heal_cast</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>治疗生效</t>
+          <t>治疗术释放</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>res://sound/sfx/spell_heal_tick.wav</t>
+          <t>res://sound/sfx/spell_heal_cast.wav</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -6466,38 +6466,38 @@
         <v>0</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>-12</v>
+        <v>-8</v>
       </c>
       <c r="J74" s="2" t="n">
         <v>0.98</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="L74" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M74" s="2" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>0.10-0.25</t>
+          <t>0.20-0.45</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>heal amount applied</t>
+          <t>heal card released</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
         <is>
-          <t>温和微光声；如果治疗多次跳数，播放要克制。</t>
+          <t>柔和的圣洁/绿色魔法展开声。</t>
         </is>
       </c>
       <c r="R74" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
     <row r="75" ht="42" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>spell_lightning_cast</t>
+          <t>spell_heal_end</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>闪电释放</t>
+          <t>治疗结束</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>res://sound/sfx/spell_lightning_cast.wav</t>
+          <t>res://sound/sfx/spell_heal_end.wav</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -6546,38 +6546,38 @@
         <v>0</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>-6</v>
+        <v>-10</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="L75" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M75" s="2" t="n">
-        <v>80</v>
+        <v>35</v>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>0.20-0.45</t>
+          <t>0.20-0.40</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>lightning card released</t>
+          <t>future heal over-time ends</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
         <is>
-          <t>雷击前的空气蓄能声。</t>
+          <t>柔和收束的微光声，供后续持续治疗版本使用。</t>
         </is>
       </c>
       <c r="R75" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
     <row r="76" ht="42" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>spell_lightning_impact</t>
+          <t>spell_heal_tick</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>闪电命中</t>
+          <t>治疗生效</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6614,7 +6614,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>res://sound/sfx/spell_lightning_impact.wav</t>
+          <t>res://sound/sfx/spell_heal_tick.wav</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -6626,38 +6626,38 @@
         <v>0</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>-3.5</v>
+        <v>-12</v>
       </c>
       <c r="J76" s="2" t="n">
         <v>0.98</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="L76" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M76" s="2" t="n">
-        <v>95</v>
+        <v>35</v>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>0.45-0.90</t>
+          <t>0.10-0.25</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>lightning hit</t>
+          <t>heal amount applied</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
         <is>
-          <t>大雷击裂响加短尾音，必须清楚但不能盖住结算音。</t>
+          <t>温和微光声；如果治疗多次跳数，播放要克制。</t>
         </is>
       </c>
       <c r="R76" s="2" t="inlineStr">
@@ -6669,12 +6669,12 @@
     <row r="77" ht="42" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>spell_log_impact</t>
+          <t>spell_lightning_cast</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>滚石/滚木撞击</t>
+          <t>闪电释放</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6694,7 +6694,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>res://sound/sfx/spell_log_impact.wav</t>
+          <t>res://sound/sfx/spell_lightning_cast.wav</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -6709,20 +6709,20 @@
         <v>-6</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="L77" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M77" s="2" t="n">
         <v>80</v>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>0.25-0.55</t>
+          <t>0.20-0.45</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>rolling boulder impact</t>
+          <t>lightning card released</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
         <is>
-          <t>石块挤压和单位被撞开的冲击声。</t>
+          <t>雷击前的空气蓄能声。</t>
         </is>
       </c>
       <c r="R77" s="2" t="inlineStr">
@@ -6749,12 +6749,12 @@
     <row r="78" ht="42" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>spell_log_roll</t>
+          <t>spell_lightning_impact</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>滚石/滚木移动</t>
+          <t>闪电命中</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6774,7 +6774,7 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>res://sound/sfx/spell_log_roll.wav</t>
+          <t>res://sound/sfx/spell_lightning_impact.wav</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -6786,38 +6786,38 @@
         <v>0</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>-9</v>
+        <v>-3.5</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>3</v>
       </c>
       <c r="M78" s="2" t="n">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>0.35-0.80</t>
+          <t>0.45-0.90</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>rolling boulder/log travel</t>
+          <t>lightning hit</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
         <is>
-          <t>石头或木头滚过泥土、鹅卵石的声音。</t>
+          <t>大雷击裂响加短尾音，必须清楚但不能盖住结算音。</t>
         </is>
       </c>
       <c r="R78" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
     <row r="79" ht="42" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>spell_zap_cast</t>
+          <t>spell_log_impact</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>电击释放</t>
+          <t>滚石/滚木撞击</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>res://sound/sfx/spell_zap_cast.wav</t>
+          <t>res://sound/sfx/spell_log_impact.wav</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -6866,10 +6866,10 @@
         <v>0</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.98</v>
+        <v>0.96</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>1.04</v>
@@ -6882,7 +6882,7 @@
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>0.08-0.20</t>
+          <t>0.25-0.55</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>zap card released</t>
+          <t>rolling boulder impact</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
         <is>
-          <t>紧凑电流起手声，动作要极短。</t>
+          <t>石块挤压和单位被撞开的冲击声。</t>
         </is>
       </c>
       <c r="R79" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
     <row r="80" ht="42" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>spell_zap_impact</t>
+          <t>spell_log_roll</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>电击命中</t>
+          <t>滚石/滚木移动</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>res://sound/sfx/spell_zap_impact.wav</t>
+          <t>res://sound/sfx/spell_log_roll.wav</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -6946,48 +6946,208 @@
         <v>0</v>
       </c>
       <c r="I80" s="2" t="n">
+        <v>-9</v>
+      </c>
+      <c r="J80" s="2" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="K80" s="2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M80" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>0.35-0.80</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>rolling boulder/log travel</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>石头或木头滚过泥土、鹅卵石的声音。</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr">
+        <is>
+          <t>未入库；待制作/采购音频文件</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="42" customHeight="1">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>spell_zap_cast</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>电击释放</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>sfx</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>spell</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>SFX</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>res://sound/sfx/spell_zap_cast.wav</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>-7</v>
+      </c>
+      <c r="J81" s="2" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="K81" s="2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M81" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>0.08-0.20</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>zap card released</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>紧凑电流起手声，动作要极短。</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr">
+        <is>
+          <t>未入库；待制作/采购音频文件</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="42" customHeight="1">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>spell_zap_impact</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>电击命中</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>sfx</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>spell</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>SFX</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>res://sound/sfx/spell_zap_impact.wav</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I82" s="2" t="n">
         <v>-6</v>
       </c>
-      <c r="J80" s="2" t="n">
+      <c r="J82" s="2" t="n">
         <v>0.98</v>
       </c>
-      <c r="K80" s="2" t="n">
+      <c r="K82" s="2" t="n">
         <v>1.05</v>
       </c>
-      <c r="L80" s="2" t="n">
+      <c r="L82" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="M80" s="2" t="n">
+      <c r="M82" s="2" t="n">
         <v>85</v>
       </c>
-      <c r="N80" s="2" t="inlineStr">
+      <c r="N82" s="2" t="inlineStr">
         <is>
           <t>0.12-0.30</t>
         </is>
       </c>
-      <c r="O80" s="2" t="inlineStr">
+      <c r="O82" s="2" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="P80" s="2" t="inlineStr">
+      <c r="P82" s="2" t="inlineStr">
         <is>
           <t>zap direct hit</t>
         </is>
       </c>
-      <c r="Q80" s="2" t="inlineStr">
+      <c r="Q82" s="2" t="inlineStr">
         <is>
           <t>短促电流爆点和噼啪声。</t>
         </is>
       </c>
-      <c r="R80" s="2" t="inlineStr">
+      <c r="R82" s="2" t="inlineStr">
         <is>
           <t>未入库；待制作/采购音频文件</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R80"/>
+  <autoFilter ref="A1:R82"/>
   <dataValidations count="4">
     <dataValidation sqref="C2:C500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>=_Enums!$A$2:$A$6</formula1>
